--- a/data/trans_orig/P44C-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P44C-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la persona que le recomendó realizarse la prueba de Cáncer de colon en 2012</t>
+          <t>Población según la persona que le recomendó realizarse la prueba de Cáncer de colon en 2012 (tasa de respuesta: 98,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4298</t>
+          <t>5538</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,62 +767,62 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>953</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1817</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4782</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>3,02%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>11,15%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>953</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>5752</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>3,02%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>15,18%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>911</t>
+          <t>916</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7060</t>
+          <t>7116</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,44%</t>
+          <t>46,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3097</t>
+          <t>3087</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11228</t>
+          <t>11173</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>68,86%</t>
+          <t>68,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5188</t>
+          <t>5757</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15468</t>
+          <t>16541</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>49,09%</t>
+          <t>52,5%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5020</t>
+          <t>5066</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12315</t>
+          <t>12303</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>81,01%</t>
+          <t>80,94%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2874</t>
+          <t>2909</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10272</t>
+          <t>10276</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>62,99%</t>
+          <t>63,01%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>9399</t>
+          <t>9662</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>20456</t>
+          <t>20676</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>65,62%</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6232</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>968</t>
+          <t>979</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>7149</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>43,62%</t>
+          <t>43,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>1079</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10333</t>
+          <t>10450</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>33,17%</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10555</t>
+          <t>10477</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>38,6%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5680</t>
+          <t>4718</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>12752</t>
+          <t>12449</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,23%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2245</t>
+          <t>2192</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13244</t>
+          <t>13225</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>48,43%</t>
+          <t>48,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7473</t>
+          <t>6798</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19323</t>
+          <t>18628</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>51,69%</t>
+          <t>49,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11460</t>
+          <t>12814</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27922</t>
+          <t>27864</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,13%</t>
+          <t>43,04%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7290</t>
+          <t>6948</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18323</t>
+          <t>18189</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>67,0%</t>
+          <t>66,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10790</t>
+          <t>10641</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23060</t>
+          <t>23487</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>61,68%</t>
+          <t>62,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>21347</t>
+          <t>22792</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>39441</t>
+          <t>38884</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>60,93%</t>
+          <t>60,07%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1855</t>
+          <t>1897</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10858</t>
+          <t>10988</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>40,18%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3107</t>
+          <t>2366</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12454</t>
+          <t>12631</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>33,79%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>6336</t>
+          <t>6262</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>19978</t>
+          <t>18966</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>29,3%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2269</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1104</t>
+          <t>1085</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>11007</t>
+          <t>10352</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>37,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1091</t>
+          <t>1061</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>12700</t>
+          <t>12147</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>21,68%</t>
         </is>
       </c>
     </row>
@@ -1983,12 +1983,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5472</t>
+          <t>5018</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17295</t>
+          <t>17449</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1998,12 +1998,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>60,42%</t>
+          <t>60,96%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3520</t>
+          <t>3056</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>14075</t>
+          <t>13472</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2033,12 +2033,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>51,36%</t>
+          <t>49,16%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>11079</t>
+          <t>11344</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>26756</t>
+          <t>26709</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>47,75%</t>
+          <t>47,67%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8514</t>
+          <t>8153</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20570</t>
+          <t>20788</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>71,86%</t>
+          <t>72,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6167</t>
+          <t>6026</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16845</t>
+          <t>17121</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>61,47%</t>
+          <t>62,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>18660</t>
+          <t>18282</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>35005</t>
+          <t>34853</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>62,48%</t>
+          <t>62,2%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8389</t>
+          <t>8120</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>973</t>
+          <t>990</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10595</t>
+          <t>9816</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2991</t>
+          <t>2994</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>14300</t>
+          <t>14841</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>26,49%</t>
         </is>
       </c>
     </row>
@@ -2444,7 +2444,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9281</t>
+          <t>9596</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4149</t>
+          <t>5145</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10808</t>
+          <t>10967</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,81%</t>
         </is>
       </c>
     </row>
@@ -2552,12 +2552,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3845</t>
+          <t>3871</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>14988</t>
+          <t>14697</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2587,12 +2587,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4212</t>
+          <t>4590</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>15360</t>
+          <t>15304</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>53,04%</t>
+          <t>52,84%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>10333</t>
+          <t>10178</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>25582</t>
+          <t>24959</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>35,98%</t>
         </is>
       </c>
     </row>
@@ -2665,12 +2665,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>17852</t>
+          <t>18099</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>31944</t>
+          <t>31214</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>44,78%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>79,04%</t>
+          <t>77,23%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2700,12 +2700,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5633</t>
+          <t>5925</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>16467</t>
+          <t>16761</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>56,86%</t>
+          <t>57,87%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>28029</t>
+          <t>27688</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>45037</t>
+          <t>45057</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>39,91%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>64,91%</t>
+          <t>64,94%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1284</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10597</t>
+          <t>10921</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3312</t>
+          <t>3851</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14181</t>
+          <t>13737</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>48,96%</t>
+          <t>47,43%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6814</t>
+          <t>7141</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>20868</t>
+          <t>21058</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>30,35%</t>
         </is>
       </c>
     </row>
@@ -3008,12 +3008,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>972</t>
+          <t>973</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>16667</t>
+          <t>15707</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3043,12 +3043,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2115</t>
+          <t>2033</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>13588</t>
+          <t>14210</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>5443</t>
+          <t>5485</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>22392</t>
+          <t>23660</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,67%</t>
         </is>
       </c>
     </row>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>19215</t>
+          <t>18942</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>38664</t>
+          <t>39232</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>27821</t>
+          <t>26793</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>47349</t>
+          <t>46565</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>42,31%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>51876</t>
+          <t>51024</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>80343</t>
+          <t>80301</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>36,23%</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>50909</t>
+          <t>51277</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>73194</t>
+          <t>74781</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>45,95%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>65,59%</t>
+          <t>67,02%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>34841</t>
+          <t>35205</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>55452</t>
+          <t>55268</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>50,38%</t>
+          <t>50,22%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>90228</t>
+          <t>91409</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>121839</t>
+          <t>123486</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>41,24%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>54,97%</t>
+          <t>55,71%</t>
         </is>
       </c>
     </row>
@@ -3347,12 +3347,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>8825</t>
+          <t>8885</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>24318</t>
+          <t>23998</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>13309</t>
+          <t>13852</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>31417</t>
+          <t>31350</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>27773</t>
+          <t>27682</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>50774</t>
+          <t>50530</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>22,8%</t>
         </is>
       </c>
     </row>
@@ -3614,7 +3614,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la persona que le recomendó realizarse la prueba de Cáncer de colon en 2016</t>
+          <t>Población según la persona que le recomendó realizarse la prueba de Cáncer de colon en 2016 (tasa de respuesta: 96,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3809,97 +3809,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1126</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1950</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5788</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>4,56%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>6,15%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>23,43%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>1126</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4685</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>4,56%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>6108</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>2,0%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>18,96%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1126</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>5694</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>2,0%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,83%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4307</t>
+          <t>4062</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14978</t>
+          <t>14482</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,25%</t>
+          <t>45,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4333</t>
+          <t>4766</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14893</t>
+          <t>15039</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,28%</t>
+          <t>60,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11134</t>
+          <t>11741</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>26223</t>
+          <t>25624</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>45,42%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10071</t>
+          <t>9842</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>21946</t>
+          <t>21371</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>69,23%</t>
+          <t>67,41%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8761</t>
+          <t>8749</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19171</t>
+          <t>19068</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>35,41%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>77,59%</t>
+          <t>77,18%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>22351</t>
+          <t>22618</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>37172</t>
+          <t>37246</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>40,1%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>65,9%</t>
+          <t>66,03%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3074</t>
+          <t>3176</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13323</t>
+          <t>13175</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,02%</t>
+          <t>41,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3308</t>
+          <t>3164</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14191</t>
+          <t>13599</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>24,11%</t>
         </is>
       </c>
     </row>
@@ -4378,12 +4378,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>813</t>
+          <t>821</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7671</t>
+          <t>7821</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4393,12 +4393,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4983</t>
+          <t>6043</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>919</t>
+          <t>1049</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>9718</t>
+          <t>8980</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4463,12 +4463,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>12,14%</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1104</t>
+          <t>1496</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10053</t>
+          <t>10384</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2091</t>
+          <t>1981</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11796</t>
+          <t>11175</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5310</t>
+          <t>4766</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18022</t>
+          <t>16511</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>22,32%</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19416</t>
+          <t>18923</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31959</t>
+          <t>31622</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>48,18%</t>
+          <t>46,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>78,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17588</t>
+          <t>18512</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29143</t>
+          <t>29299</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>52,23%</t>
+          <t>54,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>87,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>41855</t>
+          <t>42037</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>58412</t>
+          <t>59033</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>56,58%</t>
+          <t>56,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,96%</t>
+          <t>79,8%</t>
         </is>
       </c>
     </row>
@@ -4717,12 +4717,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2904</t>
+          <t>2980</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12907</t>
+          <t>12956</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4732,12 +4732,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8345</t>
+          <t>7481</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4308</t>
+          <t>4577</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>17235</t>
+          <t>16750</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>22,64%</t>
         </is>
       </c>
     </row>
@@ -4952,7 +4952,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6769</t>
+          <t>6682</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4982,62 +4982,62 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>2197</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>2028</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>6896</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>4,15%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>9,99%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>2197</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>7391</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>4,15%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,02%</t>
         </is>
       </c>
     </row>
@@ -5060,12 +5060,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4839</t>
+          <t>4922</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15459</t>
+          <t>15359</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>47,31%</t>
+          <t>47,01%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3563</t>
+          <t>3743</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>12792</t>
+          <t>12784</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5110,12 +5110,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>63,01%</t>
+          <t>62,97%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>10615</t>
+          <t>11188</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>24810</t>
+          <t>24805</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>46,83%</t>
+          <t>46,82%</t>
         </is>
       </c>
     </row>
@@ -5173,12 +5173,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11480</t>
+          <t>11763</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23112</t>
+          <t>22931</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>36,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>70,74%</t>
+          <t>70,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>2077</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10216</t>
+          <t>10322</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5223,12 +5223,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>50,32%</t>
+          <t>50,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15828</t>
+          <t>15493</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30368</t>
+          <t>30121</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5258,12 +5258,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>57,32%</t>
+          <t>56,86%</t>
         </is>
       </c>
     </row>
@@ -5286,12 +5286,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1115</t>
+          <t>1052</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9303</t>
+          <t>9202</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5321,12 +5321,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3109</t>
+          <t>3102</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11119</t>
+          <t>11262</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5336,12 +5336,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>54,77%</t>
+          <t>55,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5418</t>
+          <t>5345</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>17583</t>
+          <t>17270</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5371,12 +5371,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>32,6%</t>
         </is>
       </c>
     </row>
@@ -5516,12 +5516,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2893</t>
+          <t>2776</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13283</t>
+          <t>13845</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5531,12 +5531,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5551,12 +5551,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1056</t>
+          <t>1044</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8890</t>
+          <t>8552</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5566,12 +5566,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5586,12 +5586,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4954</t>
+          <t>5214</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18009</t>
+          <t>17945</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5601,12 +5601,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,34%</t>
         </is>
       </c>
     </row>
@@ -5629,12 +5629,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3916</t>
+          <t>3424</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>15060</t>
+          <t>13885</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5644,12 +5644,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5664,12 +5664,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5146</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>17317</t>
+          <t>17506</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>47,85%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5699,12 +5699,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>11984</t>
+          <t>12008</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>28740</t>
+          <t>27864</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5714,12 +5714,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>30,02%</t>
         </is>
       </c>
     </row>
@@ -5742,12 +5742,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>21238</t>
+          <t>21826</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>37303</t>
+          <t>36560</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5757,12 +5757,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>66,36%</t>
+          <t>65,04%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5777,12 +5777,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>9349</t>
+          <t>9274</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>22023</t>
+          <t>22745</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>60,19%</t>
+          <t>62,17%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5812,12 +5812,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>34226</t>
+          <t>35674</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>54422</t>
+          <t>54978</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>38,44%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>58,64%</t>
+          <t>59,24%</t>
         </is>
       </c>
     </row>
@@ -5855,12 +5855,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6227</t>
+          <t>6726</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19319</t>
+          <t>20147</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5870,12 +5870,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>35,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5890,12 +5890,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2195</t>
+          <t>2259</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13913</t>
+          <t>13825</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5925,12 +5925,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>11784</t>
+          <t>11491</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>29906</t>
+          <t>27658</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>29,8%</t>
         </is>
       </c>
     </row>
@@ -6085,12 +6085,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6455</t>
+          <t>6382</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>19933</t>
+          <t>20610</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6100,12 +6100,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6120,12 +6120,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2232</t>
+          <t>2196</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>12946</t>
+          <t>11752</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6135,12 +6135,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6155,12 +6155,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>10293</t>
+          <t>10472</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>28426</t>
+          <t>27575</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6170,12 +6170,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>9,99%</t>
         </is>
       </c>
     </row>
@@ -6198,12 +6198,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>21046</t>
+          <t>22274</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>40448</t>
+          <t>41378</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6213,12 +6213,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6233,12 +6233,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>24593</t>
+          <t>24306</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>46174</t>
+          <t>45713</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>39,66%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6268,12 +6268,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>51179</t>
+          <t>51092</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>79893</t>
+          <t>80865</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>29,28%</t>
         </is>
       </c>
     </row>
@@ -6311,12 +6311,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>76343</t>
+          <t>74838</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>100789</t>
+          <t>100450</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6326,12 +6326,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>46,51%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>62,64%</t>
+          <t>62,43%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6346,12 +6346,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>47601</t>
+          <t>48465</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>70884</t>
+          <t>70419</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>41,29%</t>
+          <t>42,04%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>61,49%</t>
+          <t>61,09%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>131392</t>
+          <t>131283</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>164940</t>
+          <t>164151</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>47,54%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>59,73%</t>
+          <t>59,44%</t>
         </is>
       </c>
     </row>
@@ -6424,12 +6424,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>22313</t>
+          <t>20940</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>41449</t>
+          <t>42226</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6439,12 +6439,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6459,12 +6459,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>8496</t>
+          <t>8950</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>25185</t>
+          <t>25559</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>33488</t>
+          <t>33146</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>59805</t>
+          <t>59107</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,4%</t>
         </is>
       </c>
     </row>
@@ -6691,7 +6691,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la persona que le recomendó realizarse la prueba de Cáncer de colon en 2023</t>
+          <t>Población según la persona que le recomendó realizarse la prueba de Cáncer de colon en 2023 (tasa de respuesta: 96,16%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6886,12 +6886,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>573</t>
+          <t>471</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5654</t>
+          <t>5277</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6901,12 +6901,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6921,12 +6921,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>365</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3220</t>
+          <t>3380</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6936,12 +6936,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6956,12 +6956,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1416</t>
+          <t>1531</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6664</t>
+          <t>6952</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6971,12 +6971,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -6999,12 +6999,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10308</t>
+          <t>9863</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23015</t>
+          <t>22851</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7014,12 +7014,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7034,12 +7034,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25453</t>
+          <t>24933</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38644</t>
+          <t>37600</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>38,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>37152</t>
+          <t>37946</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>55689</t>
+          <t>56065</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,48%</t>
         </is>
       </c>
     </row>
@@ -7112,12 +7112,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>44010</t>
+          <t>43904</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>61030</t>
+          <t>60208</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7127,12 +7127,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>47,22%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>65,63%</t>
+          <t>64,75%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7147,12 +7147,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>36011</t>
+          <t>35676</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>48819</t>
+          <t>48539</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>50,24%</t>
+          <t>49,95%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>85033</t>
+          <t>84545</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>106238</t>
+          <t>105604</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>44,46%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>55,87%</t>
+          <t>55,54%</t>
         </is>
       </c>
     </row>
@@ -7225,12 +7225,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16151</t>
+          <t>15399</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30303</t>
+          <t>30536</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7240,12 +7240,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7260,12 +7260,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17027</t>
+          <t>17938</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28615</t>
+          <t>29249</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>36656</t>
+          <t>36130</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>54914</t>
+          <t>54733</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>28,78%</t>
         </is>
       </c>
     </row>
@@ -7455,12 +7455,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>190</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18100</t>
+          <t>19094</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7470,12 +7470,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7490,12 +7490,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>532</t>
+          <t>641</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5602</t>
+          <t>6264</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1405</t>
+          <t>1650</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>17691</t>
+          <t>17515</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -7568,12 +7568,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8998</t>
+          <t>8355</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>113344</t>
+          <t>111220</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7583,12 +7583,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7603,12 +7603,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21327</t>
+          <t>21785</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35093</t>
+          <t>35890</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21565</t>
+          <t>20446</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>133216</t>
+          <t>133571</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>26,17%</t>
         </is>
       </c>
     </row>
@@ -7681,12 +7681,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>175581</t>
+          <t>175516</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>366229</t>
+          <t>366069</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7696,12 +7696,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>45,82%</t>
+          <t>45,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7716,12 +7716,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>61857</t>
+          <t>61802</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>78958</t>
+          <t>78633</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>48,64%</t>
+          <t>48,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>62,08%</t>
+          <t>61,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>255844</t>
+          <t>254370</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>468197</t>
+          <t>467201</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>50,12%</t>
+          <t>49,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,53%</t>
         </is>
       </c>
     </row>
@@ -7794,12 +7794,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6545</t>
+          <t>7183</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>87580</t>
+          <t>89498</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7809,12 +7809,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7829,12 +7829,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>19654</t>
+          <t>19598</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>33723</t>
+          <t>33321</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7844,12 +7844,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7864,12 +7864,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>19058</t>
+          <t>17566</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>113036</t>
+          <t>116862</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7879,12 +7879,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,9%</t>
         </is>
       </c>
     </row>
@@ -8024,12 +8024,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>942</t>
+          <t>895</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8015</t>
+          <t>8353</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8039,12 +8039,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8059,12 +8059,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1781</t>
+          <t>1791</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7682</t>
+          <t>8157</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3849</t>
+          <t>4003</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>12865</t>
+          <t>13580</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,63%</t>
         </is>
       </c>
     </row>
@@ -8137,12 +8137,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>22223</t>
+          <t>22436</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>39344</t>
+          <t>39911</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8152,12 +8152,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>12126</t>
+          <t>12244</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>22607</t>
+          <t>22260</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8187,12 +8187,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8207,12 +8207,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>37221</t>
+          <t>37999</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>58597</t>
+          <t>57771</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8222,12 +8222,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>32,46%</t>
         </is>
       </c>
     </row>
@@ -8250,12 +8250,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>36579</t>
+          <t>36834</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>56276</t>
+          <t>55744</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8265,12 +8265,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>34,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>52,95%</t>
+          <t>52,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8285,12 +8285,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>28729</t>
+          <t>28740</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>41370</t>
+          <t>40973</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8300,12 +8300,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>40,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>57,69%</t>
+          <t>57,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8320,12 +8320,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>68470</t>
+          <t>70244</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>92134</t>
+          <t>93604</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8335,12 +8335,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>39,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>52,59%</t>
         </is>
       </c>
     </row>
@@ -8363,12 +8363,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18061</t>
+          <t>18244</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>34874</t>
+          <t>35640</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8378,12 +8378,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8398,12 +8398,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10793</t>
+          <t>10863</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21873</t>
+          <t>21306</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8413,12 +8413,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8433,12 +8433,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>32087</t>
+          <t>32042</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>51350</t>
+          <t>51549</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8448,12 +8448,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,96%</t>
         </is>
       </c>
     </row>
@@ -8593,12 +8593,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3075</t>
+          <t>3503</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12279</t>
+          <t>12688</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8608,12 +8608,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8628,12 +8628,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4423</t>
+          <t>4587</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12902</t>
+          <t>13122</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8663,12 +8663,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9779</t>
+          <t>9842</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>22487</t>
+          <t>22999</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8678,12 +8678,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,77%</t>
         </is>
       </c>
     </row>
@@ -8706,12 +8706,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>39560</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>59937</t>
+          <t>60486</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8721,12 +8721,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>34,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8741,12 +8741,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>38941</t>
+          <t>37704</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>57215</t>
+          <t>55611</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8756,12 +8756,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>33,88%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8776,12 +8776,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>84720</t>
+          <t>84909</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>112592</t>
+          <t>111094</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8791,12 +8791,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>32,68%</t>
         </is>
       </c>
     </row>
@@ -8819,12 +8819,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>74719</t>
+          <t>74024</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>97534</t>
+          <t>97069</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>42,5%</t>
+          <t>42,11%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>55,48%</t>
+          <t>55,22%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8854,12 +8854,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>78763</t>
+          <t>77627</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>97235</t>
+          <t>96809</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8869,12 +8869,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>47,29%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>59,24%</t>
+          <t>58,98%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8889,12 +8889,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>157592</t>
+          <t>158291</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>188458</t>
+          <t>188520</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8904,12 +8904,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>46,36%</t>
+          <t>46,57%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>55,44%</t>
+          <t>55,46%</t>
         </is>
       </c>
     </row>
@@ -8932,12 +8932,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25031</t>
+          <t>24305</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>41781</t>
+          <t>41829</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8967,12 +8967,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>15822</t>
+          <t>16138</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>28716</t>
+          <t>29184</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9002,12 +9002,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>45246</t>
+          <t>44971</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>67163</t>
+          <t>66378</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9017,12 +9017,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,53%</t>
         </is>
       </c>
     </row>
@@ -9162,12 +9162,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6456</t>
+          <t>5903</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>29936</t>
+          <t>30049</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9197,12 +9197,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>11112</t>
+          <t>10607</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>22684</t>
+          <t>22188</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9212,12 +9212,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9232,12 +9232,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>16308</t>
+          <t>16171</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>47437</t>
+          <t>46826</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9247,12 +9247,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -9275,12 +9275,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>49902</t>
+          <t>58533</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>206973</t>
+          <t>206265</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9310,12 +9310,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>109448</t>
+          <t>109523</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>137542</t>
+          <t>136271</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9325,12 +9325,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9345,12 +9345,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>132329</t>
+          <t>144870</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>328199</t>
+          <t>331605</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9360,12 +9360,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>27,21%</t>
         </is>
       </c>
     </row>
@@ -9388,12 +9388,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>361880</t>
+          <t>364625</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>657643</t>
+          <t>640739</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9403,12 +9403,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>47,72%</t>
+          <t>48,09%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9423,12 +9423,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>218943</t>
+          <t>219764</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>250191</t>
+          <t>250484</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>47,75%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>54,43%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9458,12 +9458,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>601049</t>
+          <t>598928</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>963009</t>
+          <t>952101</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9473,12 +9473,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>49,33%</t>
+          <t>49,15%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>79,03%</t>
+          <t>78,14%</t>
         </is>
       </c>
     </row>
@@ -9501,12 +9501,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>43719</t>
+          <t>47802</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>170456</t>
+          <t>169570</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9516,12 +9516,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9536,12 +9536,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>73611</t>
+          <t>74463</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>99064</t>
+          <t>99139</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9551,12 +9551,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9571,12 +9571,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>105672</t>
+          <t>100041</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>253621</t>
+          <t>253406</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9586,12 +9586,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,8%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P44C-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P44C-Habitat-trans_orig.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5538</t>
+          <t>4659</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4782</t>
+          <t>5004</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,88%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>916</t>
+          <t>893</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7116</t>
+          <t>6748</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,81%</t>
+          <t>44,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3087</t>
+          <t>3118</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11173</t>
+          <t>11230</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>68,52%</t>
+          <t>68,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5757</t>
+          <t>5882</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>16541</t>
+          <t>15460</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,5%</t>
+          <t>49,07%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5066</t>
+          <t>5094</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12303</t>
+          <t>12280</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>80,78%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2909</t>
+          <t>2185</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10276</t>
+          <t>10273</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>63,01%</t>
+          <t>63,0%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>9662</t>
+          <t>9715</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>20676</t>
+          <t>21194</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>67,27%</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>6283</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>41,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>979</t>
+          <t>966</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7149</t>
+          <t>7074</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>43,84%</t>
+          <t>43,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1079</t>
+          <t>2030</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10450</t>
+          <t>10280</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>32,63%</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10477</t>
+          <t>10225</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>37,39%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4718</t>
+          <t>4960</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>12449</t>
+          <t>12191</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>18,83%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2192</t>
+          <t>2282</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13225</t>
+          <t>13473</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>48,36%</t>
+          <t>49,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6798</t>
+          <t>7434</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18628</t>
+          <t>19557</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>52,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12814</t>
+          <t>12453</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27864</t>
+          <t>28397</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>43,87%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6948</t>
+          <t>7285</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18189</t>
+          <t>18299</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>66,51%</t>
+          <t>66,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10641</t>
+          <t>10796</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23487</t>
+          <t>23667</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>62,82%</t>
+          <t>63,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>22792</t>
+          <t>21390</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>38884</t>
+          <t>37484</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>60,07%</t>
+          <t>57,91%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10988</t>
+          <t>11411</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>40,18%</t>
+          <t>41,72%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2366</t>
+          <t>2279</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12631</t>
+          <t>12330</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>6262</t>
+          <t>6530</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>18966</t>
+          <t>19347</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>29,89%</t>
         </is>
       </c>
     </row>
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1085</t>
+          <t>1077</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10352</t>
+          <t>10585</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>38,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>1062</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>12147</t>
+          <t>13606</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>24,28%</t>
         </is>
       </c>
     </row>
@@ -1983,12 +1983,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5018</t>
+          <t>5007</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17449</t>
+          <t>17253</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1998,12 +1998,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>60,96%</t>
+          <t>60,28%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3056</t>
+          <t>3190</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>13472</t>
+          <t>12651</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2033,12 +2033,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>49,16%</t>
+          <t>46,16%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>11344</t>
+          <t>11000</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>26709</t>
+          <t>26436</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>47,18%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8153</t>
+          <t>8873</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20788</t>
+          <t>20832</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>72,63%</t>
+          <t>72,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6026</t>
+          <t>6730</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17121</t>
+          <t>17511</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>62,47%</t>
+          <t>63,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>18282</t>
+          <t>17947</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>34853</t>
+          <t>35040</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>62,2%</t>
+          <t>62,54%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>968</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8120</t>
+          <t>8785</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>970</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9816</t>
+          <t>10394</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2994</t>
+          <t>2899</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>14841</t>
+          <t>14119</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>25,2%</t>
         </is>
       </c>
     </row>
@@ -2444,7 +2444,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9596</t>
+          <t>9453</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5145</t>
+          <t>5132</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10967</t>
+          <t>10938</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,77%</t>
         </is>
       </c>
     </row>
@@ -2552,12 +2552,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3871</t>
+          <t>3801</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>14697</t>
+          <t>13915</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2587,12 +2587,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4590</t>
+          <t>4250</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>15304</t>
+          <t>15504</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>52,84%</t>
+          <t>53,53%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>10178</t>
+          <t>10364</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>24959</t>
+          <t>25385</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>36,59%</t>
         </is>
       </c>
     </row>
@@ -2665,12 +2665,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>18099</t>
+          <t>18506</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>31214</t>
+          <t>31967</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>45,79%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>77,23%</t>
+          <t>79,1%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2700,12 +2700,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5925</t>
+          <t>6170</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>16761</t>
+          <t>16701</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>57,87%</t>
+          <t>57,67%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>27688</t>
+          <t>27187</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>45057</t>
+          <t>45183</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>39,19%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>65,13%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1284</t>
+          <t>1313</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10921</t>
+          <t>11320</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3851</t>
+          <t>3978</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13737</t>
+          <t>14172</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>48,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7141</t>
+          <t>6908</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>21058</t>
+          <t>20915</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>30,15%</t>
         </is>
       </c>
     </row>
@@ -3008,12 +3008,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>973</t>
+          <t>965</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>15707</t>
+          <t>15220</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3043,12 +3043,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2033</t>
+          <t>2214</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>14210</t>
+          <t>13479</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>5485</t>
+          <t>5441</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>23660</t>
+          <t>23671</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,68%</t>
         </is>
       </c>
     </row>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>18942</t>
+          <t>19146</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>39232</t>
+          <t>39901</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>26793</t>
+          <t>27142</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>46565</t>
+          <t>46246</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>42,02%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>51024</t>
+          <t>50903</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>80301</t>
+          <t>79550</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>35,89%</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>51277</t>
+          <t>51999</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>74781</t>
+          <t>74225</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>45,95%</t>
+          <t>46,6%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>67,02%</t>
+          <t>66,52%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>35205</t>
+          <t>34549</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>55268</t>
+          <t>56659</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>50,22%</t>
+          <t>51,48%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>91409</t>
+          <t>92086</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>123486</t>
+          <t>124029</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>41,55%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>55,71%</t>
+          <t>55,96%</t>
         </is>
       </c>
     </row>
@@ -3347,12 +3347,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>8885</t>
+          <t>9160</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>23998</t>
+          <t>23487</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>13852</t>
+          <t>13883</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>31350</t>
+          <t>31528</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>27682</t>
+          <t>26805</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>50530</t>
+          <t>50495</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,78%</t>
         </is>
       </c>
     </row>
@@ -3849,7 +3849,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5788</t>
+          <t>6343</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6108</t>
+          <t>5676</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,06%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4062</t>
+          <t>4269</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14482</t>
+          <t>13713</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>45,68%</t>
+          <t>43,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4766</t>
+          <t>4473</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15039</t>
+          <t>14578</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,87%</t>
+          <t>59,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11741</t>
+          <t>11178</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>25624</t>
+          <t>25670</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>45,51%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9842</t>
+          <t>9961</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>21371</t>
+          <t>21734</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>31,42%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>67,41%</t>
+          <t>68,56%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8749</t>
+          <t>8482</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19068</t>
+          <t>19160</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>77,55%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>22618</t>
+          <t>22383</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>37246</t>
+          <t>37002</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>39,68%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>66,03%</t>
+          <t>65,6%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3176</t>
+          <t>3051</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13175</t>
+          <t>13170</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,56%</t>
+          <t>41,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3164</t>
+          <t>3124</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13599</t>
+          <t>14015</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,85%</t>
         </is>
       </c>
     </row>
@@ -4378,12 +4378,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>821</t>
+          <t>831</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7821</t>
+          <t>7240</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4393,12 +4393,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6043</t>
+          <t>5580</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1049</t>
+          <t>920</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8980</t>
+          <t>9607</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4463,12 +4463,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,99%</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>1489</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10384</t>
+          <t>10511</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1981</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11175</t>
+          <t>11339</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>33,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4766</t>
+          <t>5146</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16511</t>
+          <t>17781</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>24,04%</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18923</t>
+          <t>19241</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31622</t>
+          <t>31437</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>46,96%</t>
+          <t>47,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>78,47%</t>
+          <t>78,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18512</t>
+          <t>18005</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29299</t>
+          <t>29371</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>54,97%</t>
+          <t>53,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>87,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>42037</t>
+          <t>41968</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>59033</t>
+          <t>58748</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>56,83%</t>
+          <t>56,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,8%</t>
+          <t>79,42%</t>
         </is>
       </c>
     </row>
@@ -4717,12 +4717,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2980</t>
+          <t>3060</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12956</t>
+          <t>12377</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4732,12 +4732,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7481</t>
+          <t>7334</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4577</t>
+          <t>4729</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>16750</t>
+          <t>16745</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -4952,7 +4952,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6682</t>
+          <t>6771</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5022,7 +5022,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6896</t>
+          <t>7707</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5037,7 +5037,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>14,55%</t>
         </is>
       </c>
     </row>
@@ -5060,12 +5060,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4922</t>
+          <t>4735</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15359</t>
+          <t>16009</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>49,0%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3743</t>
+          <t>3574</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>12784</t>
+          <t>13314</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5110,12 +5110,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>62,97%</t>
+          <t>65,58%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>11188</t>
+          <t>10390</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>24805</t>
+          <t>25292</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>46,82%</t>
+          <t>47,74%</t>
         </is>
       </c>
     </row>
@@ -5173,12 +5173,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11763</t>
+          <t>11303</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22931</t>
+          <t>22850</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>70,18%</t>
+          <t>69,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2077</t>
+          <t>2093</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10322</t>
+          <t>10605</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5223,12 +5223,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>50,84%</t>
+          <t>52,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15493</t>
+          <t>15664</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30121</t>
+          <t>30338</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5258,12 +5258,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>56,86%</t>
+          <t>57,27%</t>
         </is>
       </c>
     </row>
@@ -5286,12 +5286,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1052</t>
+          <t>1073</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9202</t>
+          <t>9331</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5321,12 +5321,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3102</t>
+          <t>2160</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11262</t>
+          <t>11170</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5336,12 +5336,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>55,47%</t>
+          <t>55,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5345</t>
+          <t>5455</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>17270</t>
+          <t>17515</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5371,12 +5371,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>33,06%</t>
         </is>
       </c>
     </row>
@@ -5516,12 +5516,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2776</t>
+          <t>2919</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13845</t>
+          <t>14041</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5531,12 +5531,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5551,12 +5551,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1044</t>
+          <t>1039</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8552</t>
+          <t>9453</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5566,12 +5566,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5586,12 +5586,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5214</t>
+          <t>5222</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>17945</t>
+          <t>17722</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5601,12 +5601,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,1%</t>
         </is>
       </c>
     </row>
@@ -5629,12 +5629,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3424</t>
+          <t>4059</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>13885</t>
+          <t>14122</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5644,12 +5644,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5664,12 +5664,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>5542</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>17506</t>
+          <t>17628</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>47,85%</t>
+          <t>48,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5699,12 +5699,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>12008</t>
+          <t>12176</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>27864</t>
+          <t>28880</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5714,12 +5714,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>31,12%</t>
         </is>
       </c>
     </row>
@@ -5742,12 +5742,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>21826</t>
+          <t>21136</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>36560</t>
+          <t>36570</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5757,12 +5757,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>65,04%</t>
+          <t>65,05%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5777,12 +5777,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>9274</t>
+          <t>9676</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>22745</t>
+          <t>23107</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>62,17%</t>
+          <t>63,16%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5812,12 +5812,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>35674</t>
+          <t>35328</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>54978</t>
+          <t>55797</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>38,07%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>59,24%</t>
+          <t>60,12%</t>
         </is>
       </c>
     </row>
@@ -5855,12 +5855,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6726</t>
+          <t>6810</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>20147</t>
+          <t>19293</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5870,12 +5870,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5890,12 +5890,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2259</t>
+          <t>2179</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13825</t>
+          <t>13789</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5925,12 +5925,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>11491</t>
+          <t>11445</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>27658</t>
+          <t>28446</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>30,65%</t>
         </is>
       </c>
     </row>
@@ -6085,12 +6085,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6382</t>
+          <t>6170</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>20610</t>
+          <t>20204</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6100,12 +6100,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6120,12 +6120,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2196</t>
+          <t>2216</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>11752</t>
+          <t>12768</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6135,12 +6135,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6155,12 +6155,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>10472</t>
+          <t>10512</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>27575</t>
+          <t>27917</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6170,12 +6170,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,11%</t>
         </is>
       </c>
     </row>
@@ -6198,12 +6198,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>22274</t>
+          <t>20249</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>41378</t>
+          <t>39915</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6213,12 +6213,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6233,12 +6233,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>24306</t>
+          <t>24081</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>45713</t>
+          <t>45580</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>39,66%</t>
+          <t>39,54%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6268,12 +6268,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>51092</t>
+          <t>50405</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>80865</t>
+          <t>79629</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>28,83%</t>
         </is>
       </c>
     </row>
@@ -6311,12 +6311,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>74838</t>
+          <t>75236</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>100450</t>
+          <t>100180</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6326,12 +6326,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>46,76%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>62,43%</t>
+          <t>62,27%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6346,12 +6346,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>48465</t>
+          <t>47841</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>70419</t>
+          <t>70864</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>41,5%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>61,09%</t>
+          <t>61,48%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>131283</t>
+          <t>130394</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>164151</t>
+          <t>163698</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>47,54%</t>
+          <t>47,22%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>59,44%</t>
+          <t>59,28%</t>
         </is>
       </c>
     </row>
@@ -6424,12 +6424,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>20940</t>
+          <t>21694</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>42226</t>
+          <t>42057</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6439,12 +6439,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6459,12 +6459,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>8950</t>
+          <t>8861</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>25559</t>
+          <t>25306</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>33146</t>
+          <t>35208</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>59107</t>
+          <t>61166</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>22,15%</t>
         </is>
       </c>
     </row>
@@ -6881,32 +6881,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2110</t>
+          <t>2227</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>471</t>
+          <t>772</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5277</t>
+          <t>5449</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6916,32 +6916,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1169</t>
+          <t>1173</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>347</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3380</t>
+          <t>3076</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6951,32 +6951,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>3279</t>
+          <t>3400</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1531</t>
+          <t>1354</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6952</t>
+          <t>6522</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -6994,32 +6994,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15808</t>
+          <t>16267</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9863</t>
+          <t>10229</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22851</t>
+          <t>24076</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7029,32 +7029,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>31046</t>
+          <t>32613</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24933</t>
+          <t>26005</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>37600</t>
+          <t>40252</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>38,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7064,32 +7064,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>46855</t>
+          <t>48879</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>37946</t>
+          <t>40353</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>56065</t>
+          <t>59914</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>28,86%</t>
         </is>
       </c>
     </row>
@@ -7107,32 +7107,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>52947</t>
+          <t>60264</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>43904</t>
+          <t>51415</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>60208</t>
+          <t>69156</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>56,94%</t>
+          <t>58,97%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>47,22%</t>
+          <t>50,31%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>64,75%</t>
+          <t>67,67%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7142,32 +7142,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>42271</t>
+          <t>47207</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>35676</t>
+          <t>39978</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>48539</t>
+          <t>55090</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>44,78%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>49,95%</t>
+          <t>52,25%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7177,32 +7177,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>95218</t>
+          <t>107472</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>84545</t>
+          <t>95780</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>105604</t>
+          <t>118985</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>50,07%</t>
+          <t>51,76%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>46,13%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>55,54%</t>
+          <t>57,31%</t>
         </is>
       </c>
     </row>
@@ -7220,32 +7220,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>22120</t>
+          <t>23438</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15399</t>
+          <t>16291</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30536</t>
+          <t>31560</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>22683</t>
+          <t>24435</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17938</t>
+          <t>18654</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29249</t>
+          <t>31589</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>44802</t>
+          <t>47872</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>36130</t>
+          <t>37934</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>54733</t>
+          <t>57621</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>27,75%</t>
         </is>
       </c>
     </row>
@@ -7333,17 +7333,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>92986</t>
+          <t>102195</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>92986</t>
+          <t>102195</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>92986</t>
+          <t>102195</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>97169</t>
+          <t>105428</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>97169</t>
+          <t>105428</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>97169</t>
+          <t>105428</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7403,17 +7403,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>190155</t>
+          <t>207623</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>190155</t>
+          <t>207623</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>190155</t>
+          <t>207623</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7450,32 +7450,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5122</t>
+          <t>6075</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>2370</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19094</t>
+          <t>12349</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7485,32 +7485,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>2424</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>656</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6264</t>
+          <t>5854</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7520,32 +7520,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>7508</t>
+          <t>8499</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1650</t>
+          <t>4261</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>17515</t>
+          <t>15653</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
+          <t>2,93%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
           <t>1,47%</t>
         </is>
       </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>5,39%</t>
         </is>
       </c>
     </row>
@@ -7563,32 +7563,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>37606</t>
+          <t>37638</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8355</t>
+          <t>28608</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>111220</t>
+          <t>48463</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>28240</t>
+          <t>30229</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21785</t>
+          <t>22915</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35890</t>
+          <t>38317</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>65846</t>
+          <t>67867</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20446</t>
+          <t>55164</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>133571</t>
+          <t>80415</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>27,72%</t>
         </is>
       </c>
     </row>
@@ -7676,32 +7676,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>310856</t>
+          <t>72410</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>175516</t>
+          <t>61107</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>366069</t>
+          <t>83156</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>81,11%</t>
+          <t>48,33%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>45,8%</t>
+          <t>40,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>55,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7711,32 +7711,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>70416</t>
+          <t>79265</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>61802</t>
+          <t>70937</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>78633</t>
+          <t>88273</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>55,37%</t>
+          <t>56,48%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>50,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>62,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>381271</t>
+          <t>151675</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>254370</t>
+          <t>137982</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>467201</t>
+          <t>166521</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>74,7%</t>
+          <t>52,28%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>49,84%</t>
+          <t>47,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>57,39%</t>
         </is>
       </c>
     </row>
@@ -7789,32 +7789,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>29649</t>
+          <t>33690</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7183</t>
+          <t>24680</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>89498</t>
+          <t>44191</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7824,32 +7824,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>26143</t>
+          <t>28414</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>19598</t>
+          <t>21206</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>33321</t>
+          <t>36030</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7859,32 +7859,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>55792</t>
+          <t>62104</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>17566</t>
+          <t>50500</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>116862</t>
+          <t>74501</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>25,68%</t>
         </is>
       </c>
     </row>
@@ -7902,17 +7902,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>383233</t>
+          <t>149813</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>383233</t>
+          <t>149813</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>383233</t>
+          <t>149813</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7937,17 +7937,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>127184</t>
+          <t>140333</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>127184</t>
+          <t>140333</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>127184</t>
+          <t>140333</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7972,17 +7972,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>510417</t>
+          <t>290145</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>510417</t>
+          <t>290145</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>510417</t>
+          <t>290145</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8019,32 +8019,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3395</t>
+          <t>3548</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>877</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8353</t>
+          <t>9145</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8054,32 +8054,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>4323</t>
+          <t>5201</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1791</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8157</t>
+          <t>9296</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>7717</t>
+          <t>8749</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4003</t>
+          <t>4634</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>13580</t>
+          <t>14827</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,34%</t>
         </is>
       </c>
     </row>
@@ -8132,32 +8132,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>30075</t>
+          <t>31602</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>22436</t>
+          <t>23196</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>39911</t>
+          <t>41983</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>35,73%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8167,32 +8167,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>17079</t>
+          <t>20353</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>12244</t>
+          <t>14795</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>22260</t>
+          <t>26492</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8202,32 +8202,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>47153</t>
+          <t>51955</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>37999</t>
+          <t>40945</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>57771</t>
+          <t>63040</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>31,21%</t>
         </is>
       </c>
     </row>
@@ -8245,32 +8245,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>46435</t>
+          <t>52394</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>36834</t>
+          <t>40773</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>55744</t>
+          <t>62574</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>44,59%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>34,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>52,45%</t>
+          <t>53,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8280,32 +8280,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>34693</t>
+          <t>40935</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>28740</t>
+          <t>33909</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>40973</t>
+          <t>47850</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>48,38%</t>
+          <t>48,46%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>40,08%</t>
+          <t>40,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>57,14%</t>
+          <t>56,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8315,32 +8315,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>81128</t>
+          <t>93329</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>70244</t>
+          <t>81994</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>93604</t>
+          <t>106405</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>45,58%</t>
+          <t>46,21%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>39,47%</t>
+          <t>40,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>52,59%</t>
+          <t>52,68%</t>
         </is>
       </c>
     </row>
@@ -8358,32 +8358,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>26372</t>
+          <t>29956</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18244</t>
+          <t>22083</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>35640</t>
+          <t>41149</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>35,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8393,32 +8393,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>15619</t>
+          <t>17988</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10863</t>
+          <t>12881</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21306</t>
+          <t>24950</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8428,32 +8428,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>41991</t>
+          <t>47943</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>32042</t>
+          <t>36290</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>51549</t>
+          <t>58649</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>29,04%</t>
         </is>
       </c>
     </row>
@@ -8471,17 +8471,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>106277</t>
+          <t>117499</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>106277</t>
+          <t>117499</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>106277</t>
+          <t>117499</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8506,17 +8506,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>71713</t>
+          <t>84477</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>71713</t>
+          <t>84477</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>71713</t>
+          <t>84477</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8541,17 +8541,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>177990</t>
+          <t>201976</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>177990</t>
+          <t>201976</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>177990</t>
+          <t>201976</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8588,32 +8588,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7018</t>
+          <t>7780</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3503</t>
+          <t>4185</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12688</t>
+          <t>14065</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8623,32 +8623,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>7926</t>
+          <t>8525</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4587</t>
+          <t>4893</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13122</t>
+          <t>13897</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8658,32 +8658,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>14944</t>
+          <t>16305</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9842</t>
+          <t>10428</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>22999</t>
+          <t>23099</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,44%</t>
         </is>
       </c>
     </row>
@@ -8701,32 +8701,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>50120</t>
+          <t>49929</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>39560</t>
+          <t>40055</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>60486</t>
+          <t>61560</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>34,41%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8736,32 +8736,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>46751</t>
+          <t>50483</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>37704</t>
+          <t>41823</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>55611</t>
+          <t>59254</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8771,32 +8771,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>96871</t>
+          <t>100412</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>84909</t>
+          <t>86431</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>111094</t>
+          <t>114449</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>31,91%</t>
         </is>
       </c>
     </row>
@@ -8814,32 +8814,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>86092</t>
+          <t>88749</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>74024</t>
+          <t>77469</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>97069</t>
+          <t>99802</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>48,97%</t>
+          <t>49,27%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>42,11%</t>
+          <t>43,01%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>55,22%</t>
+          <t>55,4%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8849,32 +8849,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>87703</t>
+          <t>96121</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>77627</t>
+          <t>85884</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>96809</t>
+          <t>105546</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>53,43%</t>
+          <t>53,84%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>47,29%</t>
+          <t>48,1%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>58,98%</t>
+          <t>59,12%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8884,32 +8884,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>173795</t>
+          <t>184870</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>158291</t>
+          <t>169885</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>188520</t>
+          <t>199915</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>51,13%</t>
+          <t>51,54%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>47,36%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>55,46%</t>
+          <t>55,74%</t>
         </is>
       </c>
     </row>
@@ -8927,32 +8927,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>32562</t>
+          <t>33681</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>24305</t>
+          <t>25719</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>41829</t>
+          <t>43148</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8962,32 +8962,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>21755</t>
+          <t>23405</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>16138</t>
+          <t>16869</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>29184</t>
+          <t>30561</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8997,32 +8997,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>54318</t>
+          <t>57087</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>44971</t>
+          <t>46221</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>66378</t>
+          <t>68762</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,17%</t>
         </is>
       </c>
     </row>
@@ -9040,17 +9040,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>175792</t>
+          <t>180139</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>175792</t>
+          <t>180139</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>175792</t>
+          <t>180139</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9075,17 +9075,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>164136</t>
+          <t>178534</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>164136</t>
+          <t>178534</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>164136</t>
+          <t>178534</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9110,17 +9110,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>339928</t>
+          <t>358673</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>339928</t>
+          <t>358673</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>339928</t>
+          <t>358673</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9157,32 +9157,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>17646</t>
+          <t>19629</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5903</t>
+          <t>12914</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>30049</t>
+          <t>29587</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9192,32 +9192,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>15803</t>
+          <t>17324</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>10607</t>
+          <t>11567</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>22188</t>
+          <t>24189</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9227,32 +9227,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>33449</t>
+          <t>36953</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>16171</t>
+          <t>27434</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>46826</t>
+          <t>47606</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -9270,32 +9270,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>133609</t>
+          <t>135435</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>58533</t>
+          <t>116336</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>206265</t>
+          <t>154372</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9305,32 +9305,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>123117</t>
+          <t>133678</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>109523</t>
+          <t>119217</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>136271</t>
+          <t>150204</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9340,32 +9340,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>256725</t>
+          <t>269113</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>144870</t>
+          <t>245856</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>331605</t>
+          <t>293577</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>27,74%</t>
         </is>
       </c>
     </row>
@@ -9383,32 +9383,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>496330</t>
+          <t>273817</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>364625</t>
+          <t>252038</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>640739</t>
+          <t>294976</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>65,45%</t>
+          <t>49,82%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>45,85%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>53,67%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9418,32 +9418,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>235084</t>
+          <t>263528</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>219764</t>
+          <t>246515</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>250484</t>
+          <t>279340</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>51,08%</t>
+          <t>51,8%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>47,75%</t>
+          <t>48,45%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>54,43%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9453,32 +9453,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>731413</t>
+          <t>537345</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>598928</t>
+          <t>510021</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>952101</t>
+          <t>564019</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>60,03%</t>
+          <t>50,77%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>49,15%</t>
+          <t>48,19%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>53,29%</t>
         </is>
       </c>
     </row>
@@ -9496,32 +9496,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>110704</t>
+          <t>120765</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>47802</t>
+          <t>104858</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>169570</t>
+          <t>139404</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9531,32 +9531,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>86199</t>
+          <t>94242</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>74463</t>
+          <t>80856</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>99139</t>
+          <t>107921</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9566,32 +9566,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>196903</t>
+          <t>215007</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>100041</t>
+          <t>193691</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>253406</t>
+          <t>237797</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>22,47%</t>
         </is>
       </c>
     </row>
@@ -9609,17 +9609,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>758288</t>
+          <t>549646</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>758288</t>
+          <t>549646</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>758288</t>
+          <t>549646</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9644,17 +9644,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>460203</t>
+          <t>508772</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>460203</t>
+          <t>508772</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>460203</t>
+          <t>508772</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -9679,17 +9679,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1218491</t>
+          <t>1058418</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1218491</t>
+          <t>1058418</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1218491</t>
+          <t>1058418</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
